--- a/Data/outputs/tablas/descripcionGEIH.xlsx
+++ b/Data/outputs/tablas/descripcionGEIH.xlsx
@@ -377,8 +377,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="C2">
         <v>0</v>
@@ -388,8 +390,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -404,8 +408,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>1</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -420,8 +426,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>1</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -436,8 +444,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>1</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -452,8 +462,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>2</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Febrero</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -468,8 +480,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>2</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Febrero</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -484,8 +498,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>2</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Febrero</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -500,8 +516,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>2</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Febrero</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -516,8 +534,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>3</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Marzo</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -532,8 +552,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>3</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Marzo</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -548,8 +570,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>3</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Marzo</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -564,8 +588,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>3</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Marzo</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -580,8 +606,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>4</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -596,8 +624,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>4</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -612,8 +642,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>4</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -628,8 +660,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>4</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -644,8 +678,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>5</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Mayo</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -660,8 +696,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>5</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mayo</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -676,8 +714,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>5</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Mayo</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -692,8 +732,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>5</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Mayo</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -708,8 +750,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>6</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Junio</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -724,8 +768,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>6</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Junio</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -740,8 +786,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>6</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Junio</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -756,8 +804,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>6</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Junio</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -772,8 +822,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>7</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Julio</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -788,8 +840,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>7</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Julio</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -804,8 +858,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>7</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Julio</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -820,8 +876,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>7</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Julio</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -836,8 +894,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>8</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -852,8 +912,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>8</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -868,8 +930,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>8</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -884,8 +948,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>8</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -900,8 +966,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>9</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Septiembre</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -916,8 +984,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>9</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Septiembre</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -932,8 +1002,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>9</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Septiembre</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -948,8 +1020,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>9</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Septiembre</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -964,8 +1038,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>10</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Octubre</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -980,8 +1056,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>10</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Octubre</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -996,8 +1074,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>10</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Octubre</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1012,8 +1092,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>10</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Octubre</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1028,8 +1110,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>11</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Noviembre</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1044,8 +1128,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>11</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Noviembre</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1060,8 +1146,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>11</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Noviembre</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1076,8 +1164,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>11</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Noviembre</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1092,8 +1182,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>12</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Diciembre</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1108,8 +1200,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>12</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Diciembre</t>
+        </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1124,8 +1218,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>12</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Diciembre</t>
+        </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1140,8 +1236,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>12</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Diciembre</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1156,8 +1254,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>2025</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Total Año 2025</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
